--- a/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
+++ b/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R64cf930c0acb4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R94218e23724b49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R43049df776c845a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rde727d2abcd741ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rce64cc0399104622"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R465d35b522fe43b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R6992dcb00f5845a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Rb68fa29b459948f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rf0a1a28bd6804651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc6213063316846ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R4e963ec514dc4826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Ra60b8ec2e6d24cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R7cc4225ec80f4098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R6b77dfdaa3e8494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rd798bd23a13d4000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R7108403431dc4b42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,6 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
@@ -235,7 +238,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="86">
+  <x:cellXfs count="89">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,6 +430,13 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1033,9 +1043,10 @@
         <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="28" customHeight="1">
+    <x:row r="23" ht="100" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>本ファイルを複製し、黄色セルを対象共通処理の仕様へ置換する。Backend、Frontend、Security、Data Access、Redis／Cache、File、Batch／Jobに適用する。処理は05のStep表へ展開する。非対象Sectionは削除するか、理由を1件記載して未使用行を削除する。Class／Method名は確定済の場合のみ記載する。</x:v>
+        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+本ファイルを複製し、黄色セルを対象共通処理の仕様へ置換する。Backend、Frontend、Security、Data Access、Redis／Cache、File、Batch／Jobに適用する。処理は05のStep表へ展開する。非対象Sectionは削除するか、理由を1件記載して未使用行を削除する。Class／Method名は確定済の場合のみ記載する。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
       <x:c r="D23" s="29"/>
@@ -1111,8 +1122,8 @@
     <x:mergeCell ref="F20:I20"/>
     <x:mergeCell ref="B10:K12"/>
     <x:mergeCell ref="F15:I15"/>
+    <x:mergeCell ref="F16:I16"/>
     <x:mergeCell ref="B23:K27"/>
-    <x:mergeCell ref="F16:I16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1483,6 +1494,36 @@
       <x:c r="H12" t="str">
         <x:v>修正済</x:v>
       </x:c>
+    </x:row>
+    <x:row r="13" ht="84" customHeight="1">
+      <x:c r="A13" s="86" t="str">
+        <x:v>Ver.1.3</x:v>
+      </x:c>
+      <x:c r="B13" s="88" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C13" s="86" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="D13" s="86" t="str">
+        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
+      </x:c>
+      <x:c r="E13" s="86" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F13" s="86" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="G13" s="86" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H13" s="86" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
+++ b/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rf0a1a28bd6804651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc6213063316846ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R4e963ec514dc4826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Ra60b8ec2e6d24cf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R7cc4225ec80f4098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R6b77dfdaa3e8494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rd798bd23a13d4000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R7108403431dc4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R64cf930c0acb4ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R94218e23724b49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R43049df776c845a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rde727d2abcd741ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rce64cc0399104622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R465d35b522fe43b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R6992dcb00f5845a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="Rb68fa29b459948f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,9 +20,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-  </x:numFmts>
   <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
@@ -238,7 +235,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="89">
+  <x:cellXfs count="86">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -430,13 +427,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1043,10 +1033,9 @@
         <x:v>&lt;&lt;記入&gt;&gt;</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="100" customHeight="1">
+    <x:row r="23" ht="28" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
-本ファイルを複製し、黄色セルを対象共通処理の仕様へ置換する。Backend、Frontend、Security、Data Access、Redis／Cache、File、Batch／Jobに適用する。処理は05のStep表へ展開する。非対象Sectionは削除するか、理由を1件記載して未使用行を削除する。Class／Method名は確定済の場合のみ記載する。</x:v>
+        <x:v>本ファイルを複製し、黄色セルを対象共通処理の仕様へ置換する。Backend、Frontend、Security、Data Access、Redis／Cache、File、Batch／Jobに適用する。処理は05のStep表へ展開する。非対象Sectionは削除するか、理由を1件記載して未使用行を削除する。Class／Method名は確定済の場合のみ記載する。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
       <x:c r="D23" s="29"/>
@@ -1122,8 +1111,8 @@
     <x:mergeCell ref="F20:I20"/>
     <x:mergeCell ref="B10:K12"/>
     <x:mergeCell ref="F15:I15"/>
+    <x:mergeCell ref="B23:K27"/>
     <x:mergeCell ref="F16:I16"/>
-    <x:mergeCell ref="B23:K27"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1494,36 +1483,6 @@
       <x:c r="H12" t="str">
         <x:v>修正済</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="84" customHeight="1">
-      <x:c r="A13" s="86" t="str">
-        <x:v>Ver.1.3</x:v>
-      </x:c>
-      <x:c r="B13" s="88" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="C13" s="86" t="str">
-        <x:v>Review</x:v>
-      </x:c>
-      <x:c r="D13" s="86" t="str">
-        <x:v>二次Review完了。設計内容変更なし。Review済／承認待ちへ整理。</x:v>
-      </x:c>
-      <x:c r="E13" s="86" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="F13" s="86" t="str">
-        <x:v>Review済</x:v>
-      </x:c>
-      <x:c r="G13" s="86" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="H13" s="86" t="str">
-        <x:v>承認待ち</x:v>
-      </x:c>
-      <x:c r="I13"/>
-      <x:c r="J13"/>
-      <x:c r="K13"/>
-      <x:c r="L13"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
+++ b/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rf0a1a28bd6804651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rc6213063316846ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R4e963ec514dc4826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Ra60b8ec2e6d24cf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R7cc4225ec80f4098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R6b77dfdaa3e8494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="Rd798bd23a13d4000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R7108403431dc4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9c7296c8ae014ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R957e9eb5495b43c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R30301071b16a4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="R9797d33ddfd141b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rb86a33c084cc4c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R9e35f536d1284a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R3a8db168f7014a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R9261bb0a56a14429"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1428,7 +1428,7 @@
         <x:v>改訂</x:v>
       </x:c>
       <x:c r="D10" s="56" t="str">
-        <x:v>共通処理IDを成果物一覧のCMN体系へ統一</x:v>
+        <x:v>共通処理IDをCMN-FE／CMN-BE／CMN-DB体系へ統一</x:v>
       </x:c>
       <x:c r="E10" s="56" t="str">
         <x:v>&lt;&lt;記入&gt;&gt;</x:v>
@@ -1819,10 +1819,10 @@
         <x:v>&lt;&lt;CMN区分・番号&gt;&gt;</x:v>
       </x:c>
       <x:c r="C9" s="81" t="str">
-        <x:v>00_詳細設計成果物一覧／03_成果物一覧</x:v>
+        <x:v>本書表紙／ファイル名</x:v>
       </x:c>
       <x:c r="D9" s="81" t="str">
-        <x:v>詳細設計成果物一覧の共通処理IDと一致する。</x:v>
+        <x:v>共通処理IDは表紙、ファイル名および本文内で一致させる。</x:v>
       </x:c>
       <x:c r="E9" s="75"/>
       <x:c r="F9" s="75"/>

--- a/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
+++ b/詳細設計/01C_共通処理詳細設計書テンプレート.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9c7296c8ae014ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R957e9eb5495b43c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R30301071b16a4145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="R9797d33ddfd141b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="Rb86a33c084cc4c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="R9e35f536d1284a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R3a8db168f7014a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R9261bb0a56a14429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R647936001c25469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb5254b99bea641ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_共通機能概要" sheetId="3" r:id="R919a250e79374b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_利用IF・依存関係" sheetId="4" r:id="Rf2a23081699c4826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_設定値・データ定義" sheetId="5" r:id="R7690a826e35a4944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_処理業務フロー" sheetId="6" r:id="Ra08a4aa5929e4caa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_例外・ログ・Security" sheetId="7" r:id="R3d68317e5fe74430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_単体テスト観点" sheetId="8" r:id="R4a4cb29d67f54663"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -945,7 +945,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="F16" s="22" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="G16" s="22"/>
       <x:c r="H16" s="22"/>
@@ -1045,7 +1045,7 @@
     </x:row>
     <x:row r="23" ht="100" customHeight="1">
       <x:c r="B23" s="29" t="str">
-        <x:v>文書状態：Review済／承認待ち。二次Review日：2026-09-30。
+        <x:v>文書状態：修正済／Review待ち。改訂日：2026-10-15。
 本ファイルを複製し、黄色セルを対象共通処理の仕様へ置換する。Backend、Frontend、Security、Data Access、Redis／Cache、File、Batch／Jobに適用する。処理は05のStep表へ展開する。非対象Sectionは削除するか、理由を1件記載して未使用行を削除する。Class／Method名は確定済の場合のみ記載する。</x:v>
       </x:c>
       <x:c r="C23" s="29"/>
@@ -1269,7 +1269,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1524,6 +1524,32 @@
       <x:c r="J13"/>
       <x:c r="K13"/>
       <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="86" t="str">
+        <x:v>Ver.1.4</x:v>
+      </x:c>
+      <x:c r="B14" s="88" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C14" s="86" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D14" s="86" t="str">
+        <x:v>実装に必要な上流事項の展開と正本位置の記載方式を明確化。</x:v>
+      </x:c>
+      <x:c r="E14" s="86" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F14" s="86" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G14" s="86" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H14" s="86" t="str">
+        <x:v>Review待ち</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1691,7 +1717,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -1713,13 +1739,13 @@
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="21" t="str">
-        <x:v>基本設計参照</x:v>
+        <x:v>本書には共通処理の入力、出力、条件、分岐、設定、資源、異常時状態を実装可能な粒度で記載する。適用する上流規則は具体的に展開し、基本設計File／Sheet／設計ID又はCell位置を根拠として示す。</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -3109,7 +3135,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -3137,7 +3163,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -4674,7 +4700,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -4702,7 +4728,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -6207,7 +6233,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -6235,7 +6261,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -7655,7 +7681,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -7683,7 +7709,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
@@ -9269,7 +9295,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
-        <x:v>Ver.1.3</x:v>
+        <x:v>Ver.1.4</x:v>
       </x:c>
       <x:c r="D4" s="39"/>
       <x:c r="E4" s="39"/>
@@ -9297,7 +9323,7 @@
         <x:v>基本設計参照</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
-        <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
+        <x:v>&lt;&lt;基本設計File／Sheet／設計ID又はCell位置&gt;&gt;</x:v>
       </x:c>
       <x:c r="D5" s="39" t="str">
         <x:v>&lt;&lt;基本設計書番号／Sheet／行&gt;&gt;</x:v>
